--- a/Historico.xlsx
+++ b/Historico.xlsx
@@ -635,64 +635,64 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B2" t="n">
-        <v>52020962</v>
+        <v>53824013</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>3.26181042317192</v>
+        <v>3.40729531415315</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>52.525953864521</v>
-      </c>
-      <c r="H2" t="n">
-        <v>5.27380990982056</v>
-      </c>
+        <v>52.8248609036268</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>1137000</v>
+        <v>1284000</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>48.8</v>
+        <v>55</v>
       </c>
       <c r="M2" t="n">
-        <v>30.9523811340332</v>
+        <v>26.96</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.653441548347473</v>
+        <v>-0.2709021</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.709870934486389</v>
+        <v>-0.4379755</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.222135826945305</v>
+        <v>-0.2948929</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.395599663257599</v>
+        <v>-0.4128225</v>
       </c>
       <c r="R2" t="n">
-        <v>36.6666679382324</v>
+        <v>36.76</v>
       </c>
       <c r="S2" t="n">
-        <v>7.20094334280093</v>
+        <v>6.38934150079073</v>
       </c>
       <c r="T2" t="n">
-        <v>5.588169529592981</v>
+        <v>5.17476629301493</v>
       </c>
       <c r="U2" t="n">
-        <v>50.6761681803936</v>
+        <v>52.2258564710625</v>
       </c>
       <c r="V2" t="n">
-        <v>23.8834363913571</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
+        <v>25.3153858621226</v>
+      </c>
+      <c r="W2" t="n">
+        <v>47.26693</v>
+      </c>
       <c r="X2" t="n">
-        <v>2.185657389419288</v>
+        <v>2.385552337021025</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -746,11 +746,7 @@
           <t>ALTO ⭡</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>ALTO ⭡</t>
-        </is>
-      </c>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr">
         <is>
@@ -772,68 +768,70 @@
           <t>ALTO ⭡</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>ALTO ⭡</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B3" t="n">
-        <v>53824013</v>
+        <v>55652890</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>3.40729531415315</v>
+        <v>3.3414302210835</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>52.8248609036268</v>
+        <v>53.0736238495431</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>1284000</v>
+        <v>1327000</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>55</v>
+        <v>56.6</v>
       </c>
       <c r="M3" t="n">
-        <v>28.5714282989502</v>
+        <v>24.51</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.606901288032532</v>
+        <v>-0.2821724</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.531419515609741</v>
+        <v>-0.3582731</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.223375126719475</v>
+        <v>-0.3440651</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.396327495574951</v>
+        <v>-0.4645443</v>
       </c>
       <c r="R3" t="n">
-        <v>34.2857131958008</v>
+        <v>30.88</v>
       </c>
       <c r="S3" t="n">
-        <v>6.38934150079073</v>
+        <v>5.65469286500665</v>
       </c>
       <c r="T3" t="n">
-        <v>5.174766293014932</v>
+        <v>5.3187160522893</v>
       </c>
       <c r="U3" t="n">
-        <v>52.2258564710625</v>
+        <v>53.7768153446022</v>
       </c>
       <c r="V3" t="n">
-        <v>25.3153858621226</v>
-      </c>
-      <c r="W3" t="n">
-        <v>47.26693</v>
-      </c>
+        <v>26.7585271322434</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>2.385552337021025</v>
+        <v>2.384422444189331</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -857,7 +855,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>MUY ALTO ⚠</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -909,70 +907,74 @@
           <t>ALTO ⭡</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>ALTO ⭡</t>
-        </is>
-      </c>
+      <c r="AQ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B4" t="n">
-        <v>55652890</v>
+        <v>57437145</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>3.3414302210835</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+        <v>3.15572113764533</v>
+      </c>
+      <c r="E4" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>58.9</v>
+      </c>
       <c r="G4" t="n">
-        <v>53.0736238495431</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>53.2535161109898</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.05194997787476</v>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>1327000</v>
+        <v>1506000</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>56.6</v>
+        <v>56.1</v>
       </c>
       <c r="M4" t="n">
-        <v>26.1904754638672</v>
+        <v>24.88</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.682187914848328</v>
+        <v>-0.399803</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.486995428800583</v>
+        <v>-0.3476867</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.278485029935837</v>
+        <v>-0.5042087</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.470542252063751</v>
+        <v>-0.5345038</v>
       </c>
       <c r="R4" t="n">
-        <v>29.5238094329834</v>
+        <v>28.92</v>
       </c>
       <c r="S4" t="n">
-        <v>5.65469286500665</v>
+        <v>4.75998593558216</v>
       </c>
       <c r="T4" t="n">
-        <v>5.318716052289308</v>
+        <v>3.49445848856181</v>
       </c>
       <c r="U4" t="n">
-        <v>53.7768153446022</v>
+        <v>55.3281861083023</v>
       </c>
       <c r="V4" t="n">
-        <v>26.7585271322434</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
+        <v>28.2133927251419</v>
+      </c>
+      <c r="W4" t="n">
+        <v>43.0093</v>
+      </c>
       <c r="X4" t="n">
-        <v>2.384422444189331</v>
+        <v>2.62199661908683</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -996,7 +998,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>MUY ALTO ⚠</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -1006,27 +1008,35 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
+          <t>BAJO ⭣</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>ALTO ⭡</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
           <t>MEDIO ⭤</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>ALTO ⭡</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>MEDIO ⭤</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>ALTO ⭡</t>
+        </is>
+      </c>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>ALTO ⭡</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>ALTO ⭡</t>
+        </is>
+      </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr">
         <is>
@@ -1048,74 +1058,70 @@
           <t>ALTO ⭡</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>ALTO ⭡</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B5" t="n">
-        <v>57437145</v>
+        <v>59174891</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>3.15572113764533</v>
-      </c>
-      <c r="E5" t="n">
-        <v>51.3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>59.2</v>
-      </c>
+        <v>2.98060939385811</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>53.2535161109898</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4.05194997787476</v>
-      </c>
+        <v>53.4064794475076</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>1506000</v>
+        <v>1527000</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>56.1</v>
+        <v>56.3</v>
       </c>
       <c r="M5" t="n">
-        <v>25.4716987609863</v>
+        <v>25.73</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.779476463794708</v>
+        <v>-0.4575062</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.475951611995697</v>
+        <v>-0.3033336</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.380523890256882</v>
+        <v>-0.5704511</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.573051035404205</v>
+        <v>-0.5669354</v>
       </c>
       <c r="R5" t="n">
-        <v>29.0476188659668</v>
+        <v>23.53</v>
       </c>
       <c r="S5" t="n">
-        <v>4.75998593558216</v>
+        <v>4.59485426006108</v>
       </c>
       <c r="T5" t="n">
-        <v>3.494458488561813</v>
+        <v>3.4642805799902</v>
       </c>
       <c r="U5" t="n">
-        <v>55.3281861083023</v>
+        <v>56.8787467857379</v>
       </c>
       <c r="V5" t="n">
-        <v>28.2133927251419</v>
-      </c>
-      <c r="W5" t="n">
-        <v>43.0093</v>
-      </c>
+        <v>29.6802357492442</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>2.62199661908683</v>
+        <v>2.580486375547358</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1144,7 +1150,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>MUY ALTO ⚠</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1162,22 +1168,14 @@
           <t>MEDIO ⭤</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>ALTO ⭡</t>
-        </is>
-      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr">
         <is>
           <t>ALTO ⭡</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>ALTO ⭡</t>
-        </is>
-      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr">
         <is>
@@ -1199,71 +1197,69 @@
           <t>ALTO ⭡</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>ALTO ⭡</t>
-        </is>
-      </c>
+      <c r="AQ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B6" t="n">
-        <v>59174891</v>
+        <v>60972798</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>2.98060939385811</v>
+        <v>2.99305168844906</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>53.4064794475076</v>
+        <v>53.6083841322846</v>
       </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="n">
-        <v>1527000</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>1.792</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>82.84999999999999</v>
+      </c>
       <c r="L6" t="n">
-        <v>56.3</v>
+        <v>57.6</v>
       </c>
       <c r="M6" t="n">
-        <v>30.6603775024414</v>
+        <v>22.33</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.854386746883392</v>
+        <v>-0.4372962</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.420570701360703</v>
+        <v>-0.2744294</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.521158754825592</v>
+        <v>-0.6863458</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.567784249782562</v>
+        <v>-0.5711761</v>
       </c>
       <c r="R6" t="n">
-        <v>28.0952377319336</v>
+        <v>24.02</v>
       </c>
       <c r="S6" t="n">
-        <v>4.59485426006108</v>
+        <v>3.74921291744897</v>
       </c>
       <c r="T6" t="n">
-        <v>3.464280579990205</v>
+        <v>3.29029062798325</v>
       </c>
       <c r="U6" t="n">
-        <v>56.8787467857379</v>
+        <v>58.4288709914851</v>
       </c>
       <c r="V6" t="n">
-        <v>29.6802357492442</v>
-      </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="n">
-        <v>2.580486375547358</v>
-      </c>
+        <v>31.1602899873696</v>
+      </c>
+      <c r="W6" t="n">
+        <v>40.88048</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
           <t>ALTO ⭡</t>
@@ -1286,12 +1282,12 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>MUY ALTO ⚠</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>MUY ALTO ⚠</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -1317,12 +1313,12 @@
         </is>
       </c>
       <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>BAJO ⭣</t>
-        </is>
-      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>ALTO ⭡</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr">
         <is>
           <t>ALTO ⭡</t>
@@ -1338,68 +1334,64 @@
           <t>ALTO ⭡</t>
         </is>
       </c>
-      <c r="AQ6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>ALTO ⭡</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B7" t="n">
-        <v>60972798</v>
+        <v>62830412</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>2.99305168844906</v>
+        <v>3.00113934816488</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>53.6083841322846</v>
+        <v>53.839348530772</v>
       </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="n">
-        <v>1.792</v>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>82.84999999999999</v>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>57.6</v>
+        <v>58.7</v>
       </c>
       <c r="M7" t="n">
-        <v>27.3584899902344</v>
+        <v>25.24</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.73927241563797</v>
+        <v>-0.4300406</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.405753612518311</v>
+        <v>-0.3574141</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.735241413116455</v>
+        <v>-0.7662779</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.615206003189087</v>
+        <v>-0.5597629</v>
       </c>
       <c r="R7" t="n">
-        <v>26.1904754638672</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.74921291744897</v>
-      </c>
+        <v>25.98</v>
+      </c>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="n">
-        <v>3.290290627983255</v>
+        <v>3.69091958802198</v>
       </c>
       <c r="U7" t="n">
-        <v>58.4288709914851</v>
+        <v>59.9769893426504</v>
       </c>
       <c r="V7" t="n">
-        <v>31.1602899873696</v>
-      </c>
-      <c r="W7" t="n">
-        <v>40.88048</v>
-      </c>
+        <v>32.6535108479798</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1431,11 +1423,7 @@
           <t>ALTO ⭡</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>BAJO ⭣</t>
-        </is>
-      </c>
+      <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
           <t>ALTO ⭡</t>
@@ -1454,11 +1442,7 @@
         </is>
       </c>
       <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>ALTO ⭡</t>
-        </is>
-      </c>
+      <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr">
         <is>
@@ -1475,64 +1459,64 @@
           <t>ALTO ⭡</t>
         </is>
       </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>ALTO ⭡</t>
-        </is>
-      </c>
+      <c r="AQ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B8" t="n">
-        <v>62830412</v>
+        <v>64711821</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>3.00113934816488</v>
+        <v>2.95046658393064</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>53.839348530772</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>54.0487270478758</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6.54216003417969</v>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>58.7</v>
+        <v>58.2</v>
       </c>
       <c r="M8" t="n">
-        <v>34.4339637756348</v>
+        <v>29.13</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.648341059684753</v>
+        <v>-0.3739372</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.39461013674736</v>
+        <v>-0.3658779</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7145538926124571</v>
+        <v>-0.7167618</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.551462709903717</v>
+        <v>-0.5459878</v>
       </c>
       <c r="R8" t="n">
-        <v>29.0476188659668</v>
+        <v>31.37</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="n">
-        <v>3.690919588021988</v>
+        <v>4.35027204269101</v>
       </c>
       <c r="U8" t="n">
-        <v>59.9769893426504</v>
+        <v>61.5231007781577</v>
       </c>
       <c r="V8" t="n">
-        <v>32.6535108479798</v>
-      </c>
-      <c r="W8" t="inlineStr"/>
+        <v>34.1608687863697</v>
+      </c>
+      <c r="W8" t="n">
+        <v>70.08584999999999</v>
+      </c>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1582,12 +1566,16 @@
           <t>ALTO ⭡</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>ALTO ⭡</t>
+        </is>
+      </c>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>MEDIO ⭤</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1600,64 +1588,64 @@
           <t>ALTO ⭡</t>
         </is>
       </c>
-      <c r="AQ8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>ALTO ⭡</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B9" t="n">
-        <v>64711821</v>
+        <v>66617606</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>2.95046658393064</v>
+        <v>2.90250073555304</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>54.0487270478758</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6.54216003417969</v>
-      </c>
+        <v>54.2329053806519</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>58.2</v>
+        <v>58</v>
       </c>
       <c r="M9" t="n">
-        <v>37.2641525268555</v>
+        <v>37.38</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.460365831851959</v>
+        <v>-0.3471089</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.354882270097733</v>
+        <v>-0.3526308</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.65319699048996</v>
+        <v>-0.6563494</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.462281912565231</v>
+        <v>-0.4879775</v>
       </c>
       <c r="R9" t="n">
-        <v>30.1886787414551</v>
+        <v>33.33</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="n">
-        <v>4.350272042691012</v>
+        <v>3.79923291384916</v>
       </c>
       <c r="U9" t="n">
-        <v>61.5231007781577</v>
+        <v>63.0660884066509</v>
       </c>
       <c r="V9" t="n">
-        <v>34.1608687863697</v>
-      </c>
-      <c r="W9" t="n">
-        <v>70.08584999999999</v>
-      </c>
+        <v>35.6824982712263</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1707,11 +1695,7 @@
           <t>ALTO ⭡</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>ALTO ⭡</t>
-        </is>
-      </c>
+      <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr">
@@ -1729,62 +1713,62 @@
           <t>ALTO ⭡</t>
         </is>
       </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>ALTO ⭡</t>
-        </is>
-      </c>
+      <c r="AQ9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B10" t="n">
-        <v>66617606</v>
+        <v>68560157</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>2.90250073555304</v>
+        <v>2.87426672866542</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>54.2329053806519</v>
+        <v>54.4188908435551</v>
       </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>2.431</v>
+      </c>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>85.28700000000001</v>
+      </c>
       <c r="L10" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M10" t="n">
-        <v>44.0758285522461</v>
+        <v>31.55</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.455080926418304</v>
+        <v>-0.2750894</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.319897323846817</v>
+        <v>-0.3115302</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.533726751804352</v>
+        <v>-0.6952947</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.373498290777206</v>
+        <v>-0.5243233</v>
       </c>
       <c r="R10" t="n">
-        <v>30.1886787414551</v>
+        <v>32.84</v>
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="n">
-        <v>3.799232913849163</v>
+        <v>3.05694676312372</v>
       </c>
       <c r="U10" t="n">
-        <v>63.0660884066509</v>
+        <v>64.6059619473789</v>
       </c>
       <c r="V10" t="n">
-        <v>35.6824982712263</v>
+        <v>37.2193614570345</v>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
@@ -1837,7 +1821,11 @@
         </is>
       </c>
       <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>ALTO ⭡</t>
+        </is>
+      </c>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr">
         <is>
@@ -1858,49 +1846,85 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B11" t="n">
-        <v>68560157</v>
+        <v>70545865</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>2.87426672866542</v>
+        <v>2.85515014149945</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>54.4188908435551</v>
+        <v>54.6177440733061</v>
       </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>2.776</v>
+      </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>83.664</v>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>27.67</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.2554783</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.3339407</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.7856796</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.5711543</v>
+      </c>
+      <c r="R11" t="n">
+        <v>33.82</v>
+      </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="n">
-        <v>3.056946763123725</v>
-      </c>
-      <c r="U11" t="n">
-        <v>64.6059619473789</v>
-      </c>
-      <c r="V11" t="n">
-        <v>37.2193614570345</v>
-      </c>
+        <v>3.32697361316105</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>ALTO ⭡</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ALTO ⭡</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>ALTO ⭡</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>ALTO ⭡</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ALTO ⭡</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>ALTO ⭡</t>
+        </is>
+      </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
@@ -1920,18 +1944,14 @@
         </is>
       </c>
       <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>ALTO ⭡</t>
+        </is>
+      </c>
       <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>MEDIO ⭤</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>ALTO ⭡</t>
-        </is>
-      </c>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr"/>
     </row>

--- a/Historico.xlsx
+++ b/Historico.xlsx
@@ -696,81 +696,81 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>MEDIO ⭤</t>
+          <t>MODERADA ⭤</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>MEDIO ⭤</t>
+          <t>MODERADA ⭤</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>BAJO ⭣</t>
+          <t>BAJA ⭣</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
     </row>
@@ -835,76 +835,76 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>MUY ALTO ⚠</t>
+          <t>CRÍTICA ⚠</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>MEDIO ⭤</t>
+          <t>MODERADA ⭤</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>MEDIO ⭤</t>
+          <t>MODERADA ⭤</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>BAJO ⭣</t>
+          <t>BAJA ⭣</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr"/>
@@ -978,89 +978,89 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>MUY ALTO ⚠</t>
+          <t>CRÍTICA ⚠</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>BAJO ⭣</t>
+          <t>BAJA ⭣</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>MEDIO ⭤</t>
+          <t>MODERADA ⭤</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>CRÍTICA ⚠</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>BAJO ⭣</t>
+          <t>BAJA ⭣</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
     </row>
@@ -1125,76 +1125,76 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>MUY ALTO ⚠</t>
+          <t>CRÍTICA ⚠</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>BAJO ⭣</t>
+          <t>BAJA ⭣</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>MEDIO ⭤</t>
+          <t>MODERADA ⭤</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>BAJO ⭣</t>
+          <t>BAJA ⭣</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr"/>
@@ -1262,81 +1262,81 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>MUY ALTO ⚠</t>
+          <t>CRÍTICA ⚠</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>MUY ALTO ⚠</t>
+          <t>CRÍTICA ⚠</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>BAJO ⭣</t>
+          <t>BAJA ⭣</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>MEDIO ⭤</t>
+          <t>MODERADA ⭤</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
     </row>
@@ -1395,50 +1395,50 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>MEDIO ⭤</t>
+          <t>MODERADA ⭤</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr"/>
@@ -1446,17 +1446,17 @@
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr"/>
@@ -1520,77 +1520,77 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>MEDIO ⭤</t>
+          <t>MODERADA ⭤</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>CRÍTICA ⚠</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>MEDIO ⭤</t>
+          <t>MODERADA ⭤</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
     </row>
@@ -1649,50 +1649,50 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>MEDIO ⭤</t>
+          <t>MODERADA ⭤</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr"/>
@@ -1700,17 +1700,17 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>MEDIO ⭤</t>
+          <t>MODERADA ⭤</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr"/>
@@ -1774,72 +1774,72 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>MEDIO ⭤</t>
+          <t>MODERADA ⭤</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>MEDIO ⭤</t>
+          <t>MODERADA ⭤</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr"/>
@@ -1897,56 +1897,56 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>MEDIO ⭤</t>
+          <t>MODERADA ⭤</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>ALTA ⭡</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr"/>

--- a/Historico.xlsx
+++ b/Historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ11"/>
+  <dimension ref="A1:AR11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -632,6 +632,11 @@
           <t>Poblacion_Urbana_cat</t>
         </is>
       </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>ALTA ⭡</t>
         </is>
       </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>África</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>África</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1063,6 +1078,11 @@
           <t>ALTA ⭡</t>
         </is>
       </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>África</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1198,6 +1218,11 @@
         </is>
       </c>
       <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>África</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1337,6 +1362,11 @@
       <c r="AQ6" t="inlineStr">
         <is>
           <t>ALTA ⭡</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>África</t>
         </is>
       </c>
     </row>
@@ -1460,6 +1490,11 @@
         </is>
       </c>
       <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>África</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1591,6 +1626,11 @@
       <c r="AQ8" t="inlineStr">
         <is>
           <t>ALTA ⭡</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>África</t>
         </is>
       </c>
     </row>
@@ -1714,6 +1754,11 @@
         </is>
       </c>
       <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>África</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1843,6 +1888,11 @@
         </is>
       </c>
       <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>África</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1954,6 +2004,11 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>África</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Historico.xlsx
+++ b/Historico.xlsx
@@ -701,81 +701,81 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>MODERADA ⭤</t>
+          <t>MEDIO ⭤</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>MODERADA ⭤</t>
+          <t>MEDIO ⭤</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>BAJA ⭣</t>
+          <t>BAJO ⭣</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -845,76 +845,76 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>CRÍTICA ⚠</t>
+          <t>MUY ALTO ⚠</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>MODERADA ⭤</t>
+          <t>MEDIO ⭤</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>MODERADA ⭤</t>
+          <t>MEDIO ⭤</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>BAJA ⭣</t>
+          <t>BAJO ⭣</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr"/>
@@ -993,89 +993,89 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>CRÍTICA ⚠</t>
+          <t>MUY ALTO ⚠</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>BAJA ⭣</t>
+          <t>BAJO ⭣</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>MODERADA ⭤</t>
+          <t>MEDIO ⭤</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>CRÍTICA ⚠</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>BAJA ⭣</t>
+          <t>BAJO ⭣</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1145,76 +1145,76 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>CRÍTICA ⚠</t>
+          <t>MUY ALTO ⚠</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>BAJA ⭣</t>
+          <t>BAJO ⭣</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>MODERADA ⭤</t>
+          <t>MEDIO ⭤</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>BAJA ⭣</t>
+          <t>BAJO ⭣</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr"/>
@@ -1287,81 +1287,81 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>CRÍTICA ⚠</t>
+          <t>MUY ALTO ⚠</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>CRÍTICA ⚠</t>
+          <t>MUY ALTO ⚠</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>BAJA ⭣</t>
+          <t>BAJO ⭣</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>MODERADA ⭤</t>
+          <t>MEDIO ⭤</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>BAJO ⭣</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1425,50 +1425,50 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>MODERADA ⭤</t>
+          <t>MEDIO ⭤</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr"/>
@@ -1476,17 +1476,17 @@
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr"/>
@@ -1555,77 +1555,77 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>MODERADA ⭤</t>
+          <t>MEDIO ⭤</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>CRÍTICA ⚠</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>MODERADA ⭤</t>
+          <t>MEDIO ⭤</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -1689,50 +1689,50 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>MODERADA ⭤</t>
+          <t>MEDIO ⭤</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr"/>
@@ -1740,17 +1740,17 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>MODERADA ⭤</t>
+          <t>MEDIO ⭤</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr"/>
@@ -1819,72 +1819,72 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>MODERADA ⭤</t>
+          <t>MEDIO ⭤</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>BAJO ⭣</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>MODERADA ⭤</t>
+          <t>MEDIO ⭤</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr"/>
@@ -1947,56 +1947,56 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>MODERADA ⭤</t>
+          <t>MEDIO ⭤</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>ALTO ⭡</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>ALTA ⭡</t>
+          <t>BAJO ⭣</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr"/>

--- a/Historico.xlsx
+++ b/Historico.xlsx
@@ -734,11 +734,7 @@
           <t>MEDIO ⭤</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>ALTO ⭡</t>
-        </is>
-      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
           <t>MEDIO ⭤</t>
@@ -878,11 +874,7 @@
           <t>MEDIO ⭤</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>ALTO ⭡</t>
-        </is>
-      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
           <t>MEDIO ⭤</t>
@@ -1026,11 +1018,7 @@
           <t>BAJO ⭣</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>ALTO ⭡</t>
-        </is>
-      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
           <t>MEDIO ⭤</t>
@@ -1049,7 +1037,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>MUY ALTO ⚠</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr"/>
@@ -1178,11 +1166,7 @@
           <t>BAJO ⭣</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>ALTO ⭡</t>
-        </is>
-      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
           <t>MEDIO ⭤</t>
@@ -1320,11 +1304,7 @@
           <t>BAJO ⭣</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>ALTO ⭡</t>
-        </is>
-      </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
           <t>MEDIO ⭤</t>
@@ -1454,11 +1434,7 @@
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>ALTO ⭡</t>
-        </is>
-      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr">
         <is>
           <t>MEDIO ⭤</t>
@@ -1584,11 +1560,7 @@
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>ALTO ⭡</t>
-        </is>
-      </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr">
         <is>
           <t>MEDIO ⭤</t>
@@ -1603,7 +1575,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>ALTO ⭡</t>
+          <t>MUY ALTO ⚠</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr"/>
@@ -1718,11 +1690,7 @@
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>ALTO ⭡</t>
-        </is>
-      </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr">
         <is>
           <t>MEDIO ⭤</t>
@@ -1848,11 +1816,7 @@
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>ALTO ⭡</t>
-        </is>
-      </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr">
         <is>
           <t>MEDIO ⭤</t>
@@ -1976,11 +1940,7 @@
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>ALTO ⭡</t>
-        </is>
-      </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr">
         <is>
           <t>MEDIO ⭤</t>
